--- a/ValueSet-i2x-tabac.xlsx
+++ b/ValueSet-i2x-tabac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-tabac.xlsx
+++ b/ValueSet-i2x-tabac.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Jeu de concept de tabacologie</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -79,6 +76,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Valueset for tobaccoology concepts in the scope of the 'Vers Un Souffle Nouveau' project</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -297,62 +297,60 @@
       <c r="A5" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>13</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>15</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>17</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -396,7 +394,7 @@
         <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
@@ -425,10 +423,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">

--- a/ValueSet-i2x-tabac.xlsx
+++ b/ValueSet-i2x-tabac.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-tabac.xlsx
+++ b/ValueSet-i2x-tabac.xlsx
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>Immutable</t>
